--- a/Tool_Master.xlsx
+++ b/Tool_Master.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1729"/>
+  <dimension ref="A1:Q1733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="K201" t="n">
-        <v>10</v>
+        <v>9.379</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="K214" t="n">
-        <v>15</v>
+        <v>14.721</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="K452" t="n">
-        <v>15</v>
+        <v>14.175</v>
       </c>
       <c r="L452" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         </is>
       </c>
       <c r="K460" t="n">
-        <v>15</v>
+        <v>13.466</v>
       </c>
       <c r="L460" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>5</v>
       </c>
       <c r="K523" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="L523" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>60</v>
       </c>
       <c r="K684" t="n">
-        <v>40</v>
+        <v>39.422</v>
       </c>
       <c r="L684" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         </is>
       </c>
       <c r="K879" t="n">
-        <v>40</v>
+        <v>39.175</v>
       </c>
       <c r="L879" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>50</v>
       </c>
       <c r="K891" t="n">
-        <v>60</v>
+        <v>58.18</v>
       </c>
       <c r="L891" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>50</v>
       </c>
       <c r="K1008" t="n">
-        <v>50</v>
+        <v>49.449</v>
       </c>
       <c r="L1008" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         </is>
       </c>
       <c r="K1052" t="n">
-        <v>59.7</v>
+        <v>59.149</v>
       </c>
       <c r="L1052" t="inlineStr">
         <is>
@@ -50464,7 +50464,7 @@
         <v>25</v>
       </c>
       <c r="K1132" t="n">
-        <v>10</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L1132" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>100</v>
       </c>
       <c r="K1166" t="n">
-        <v>10</v>
+        <v>8.465999999999999</v>
       </c>
       <c r="L1166" t="inlineStr">
         <is>
@@ -55564,7 +55564,7 @@
         </is>
       </c>
       <c r="K1259" t="n">
-        <v>40</v>
+        <v>38.466</v>
       </c>
       <c r="L1259" t="inlineStr">
         <is>
@@ -56170,7 +56170,7 @@
         </is>
       </c>
       <c r="K1273" t="n">
-        <v>50</v>
+        <v>49.279</v>
       </c>
       <c r="L1273" t="inlineStr">
         <is>
@@ -56757,7 +56757,7 @@
         </is>
       </c>
       <c r="K1289" t="n">
-        <v>1.5</v>
+        <v>-0.32</v>
       </c>
       <c r="L1289" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
       <c r="I1335" s="8" t="n"/>
       <c r="J1335" s="8" t="n"/>
       <c r="K1335" s="8" t="n">
-        <v>15</v>
+        <v>14.09</v>
       </c>
       <c r="L1335" s="8" t="inlineStr">
         <is>
@@ -62927,7 +62927,7 @@
       <c r="I1425" s="8" t="n"/>
       <c r="J1425" s="8" t="n"/>
       <c r="K1425" s="8" t="n">
-        <v>15</v>
+        <v>14.09</v>
       </c>
       <c r="L1425" s="8" t="inlineStr">
         <is>
@@ -70351,7 +70351,7 @@
       <c r="I1583" s="8" t="n"/>
       <c r="J1583" s="8" t="n"/>
       <c r="K1583" s="8" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="L1583" s="8" t="inlineStr">
         <is>
@@ -74738,7 +74738,7 @@
       <c r="I1676" s="8" t="n"/>
       <c r="J1676" s="8" t="n"/>
       <c r="K1676" s="8" t="n">
-        <v>15</v>
+        <v>14.09</v>
       </c>
       <c r="L1676" s="8" t="inlineStr">
         <is>
@@ -74913,7 +74913,7 @@
       </c>
       <c r="J1679" s="8" t="n"/>
       <c r="K1679" s="8" t="n">
-        <v>0</v>
+        <v>-1.82</v>
       </c>
       <c r="L1679" s="8" t="inlineStr">
         <is>
@@ -77217,6 +77217,202 @@
       <c r="O1729" s="8" t="n"/>
       <c r="P1729" s="8" t="n"/>
       <c r="Q1729" s="8" t="n"/>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="8" t="inlineStr">
+        <is>
+          <t>TI 3ER12UNVTX 01</t>
+        </is>
+      </c>
+      <c r="B1730" s="8" t="inlineStr">
+        <is>
+          <t>3ER12UNVTX ThreadING Insert-PVD12 TPI, VTX</t>
+        </is>
+      </c>
+      <c r="C1730" s="8" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="D1730" s="8" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E1730" s="8" t="n"/>
+      <c r="F1730" s="8" t="n"/>
+      <c r="G1730" s="8" t="inlineStr">
+        <is>
+          <t>Single Use</t>
+        </is>
+      </c>
+      <c r="H1730" s="8" t="n"/>
+      <c r="I1730" s="8" t="n"/>
+      <c r="J1730" s="8" t="n"/>
+      <c r="K1730" s="8" t="n"/>
+      <c r="L1730" s="8" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="M1730" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1730" s="8" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="O1730" s="8" t="inlineStr">
+        <is>
+          <t>VISHRUTA</t>
+        </is>
+      </c>
+      <c r="P1730" s="8" t="n"/>
+      <c r="Q1730" s="8" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="8" t="inlineStr">
+        <is>
+          <t>TP M8X1.25 180 01</t>
+        </is>
+      </c>
+      <c r="B1731" s="8" t="inlineStr">
+        <is>
+          <t>M8 X 1.25 X 180 FORM E MACHINE TAP HSS COATEDD</t>
+        </is>
+      </c>
+      <c r="C1731" s="8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D1731" s="8" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="E1731" s="8" t="n"/>
+      <c r="F1731" s="8" t="n"/>
+      <c r="G1731" s="8" t="inlineStr">
+        <is>
+          <t>Multi (Resharpening Possible)</t>
+        </is>
+      </c>
+      <c r="H1731" s="8" t="n"/>
+      <c r="I1731" s="8" t="n"/>
+      <c r="J1731" s="8" t="n"/>
+      <c r="K1731" s="8" t="n"/>
+      <c r="L1731" s="8" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="M1731" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1731" s="8" t="n"/>
+      <c r="O1731" s="8" t="inlineStr">
+        <is>
+          <t>SPURS AND THREAD SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="P1731" s="8" t="n"/>
+      <c r="Q1731" s="8" t="n">
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="8" t="inlineStr">
+        <is>
+          <t>TI WTX-CHANGE-UNI-22-DPX745 01</t>
+        </is>
+      </c>
+      <c r="B1732" s="8" t="inlineStr">
+        <is>
+          <t>WTX-CHANGE-UNI-22-DPX745</t>
+        </is>
+      </c>
+      <c r="C1732" s="8" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="D1732" s="8" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E1732" s="8" t="n"/>
+      <c r="F1732" s="8" t="n"/>
+      <c r="G1732" s="8" t="inlineStr">
+        <is>
+          <t>Single Use</t>
+        </is>
+      </c>
+      <c r="H1732" s="8" t="n"/>
+      <c r="I1732" s="8" t="n"/>
+      <c r="J1732" s="8" t="n"/>
+      <c r="K1732" s="8" t="n"/>
+      <c r="L1732" s="8" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="M1732" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1732" s="8" t="n"/>
+      <c r="O1732" s="8" t="n"/>
+      <c r="P1732" s="8" t="n"/>
+      <c r="Q1732" s="8" t="n"/>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="8" t="inlineStr">
+        <is>
+          <t>TM M27X1.5 SC 01</t>
+        </is>
+      </c>
+      <c r="B1733" s="8" t="inlineStr">
+        <is>
+          <t>M27 X 1.5 SC THREAD MILL</t>
+        </is>
+      </c>
+      <c r="C1733" s="8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D1733" s="8" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="E1733" s="8" t="n"/>
+      <c r="F1733" s="8" t="n"/>
+      <c r="G1733" s="8" t="inlineStr">
+        <is>
+          <t>Multi (Resharpening Possible)</t>
+        </is>
+      </c>
+      <c r="H1733" s="8" t="n"/>
+      <c r="I1733" s="8" t="n"/>
+      <c r="J1733" s="8" t="n"/>
+      <c r="K1733" s="8" t="n"/>
+      <c r="L1733" s="8" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="M1733" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1733" s="8" t="n"/>
+      <c r="O1733" s="8" t="n"/>
+      <c r="P1733" s="8" t="n"/>
+      <c r="Q1733" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
